--- a/Additional List.xlsx
+++ b/Additional List.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\xampp\htdocs\CertificateGenerator\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\xampp\htdocs\CPCertificateGenerator\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{CCCAF7C4-978F-4131-8881-8B99EC7B40A5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{14285407-C149-435D-8E21-D181554ED592}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13176" xr2:uid="{7942AB2F-28B4-4746-9307-5633B0FDDF5E}"/>
+    <workbookView xWindow="30240" yWindow="2310" windowWidth="21600" windowHeight="11235" xr2:uid="{7942AB2F-28B4-4746-9307-5633B0FDDF5E}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -36,21 +36,9 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5" uniqueCount="5">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1" uniqueCount="1">
   <si>
-    <t>Rithwik Komati</t>
-  </si>
-  <si>
-    <t>Om Lathigara</t>
-  </si>
-  <si>
-    <t>Darshil Sapara</t>
-  </si>
-  <si>
-    <t>Kalpesh Parmar</t>
-  </si>
-  <si>
-    <t>Rutvik Parmar</t>
+    <t>Ruhaan Pathan</t>
   </si>
 </sst>
 </file>
@@ -402,7 +390,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{05EF2F79-181F-45BE-A9BA-1BB4D355110B}">
-  <dimension ref="A1:B5"/>
+  <dimension ref="A1:B1"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="13.33203125" bestFit="1" customWidth="1"/>
@@ -416,38 +404,6 @@
         <v>1</v>
       </c>
     </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A2" t="s">
-        <v>1</v>
-      </c>
-      <c r="B2">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A3" t="s">
-        <v>2</v>
-      </c>
-      <c r="B3">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A4" t="s">
-        <v>3</v>
-      </c>
-      <c r="B4">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A5" t="s">
-        <v>4</v>
-      </c>
-      <c r="B5">
-        <v>1</v>
-      </c>
-    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
